--- a/đơn hàng tay.xlsx
+++ b/đơn hàng tay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\code py\Xử lý đơn hàng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3113BC-21F2-4E3C-9FDD-9E64278C405F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C51450-A831-477F-BFDD-C727C2050528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-615" yWindow="2940" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -109,7 +109,7 @@
     <t>C6/27 Phạm Hùng, Xã Bình Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
-    <t>P-000118340</t>
+    <t>P-000229637</t>
   </si>
 </sst>
 </file>
@@ -571,25 +571,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="2">
-        <v>46051</v>
+        <v>46182</v>
       </c>
       <c r="E2" s="2">
-        <v>46053</v>
+        <v>46184</v>
       </c>
       <c r="F2" s="9">
-        <v>300865</v>
+        <v>290320</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3">
-        <v>9292</v>
+        <v>35360</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -597,25 +597,25 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>46051</v>
+        <v>46182</v>
       </c>
       <c r="E3" s="2">
-        <v>46053</v>
+        <v>46184</v>
       </c>
       <c r="F3" s="9">
         <v>290321</v>
       </c>
       <c r="G3">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3">
-        <v>32725</v>
+        <v>35360</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -623,25 +623,25 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>46051</v>
+        <v>46182</v>
       </c>
       <c r="E4" s="2">
-        <v>46053</v>
+        <v>46184</v>
       </c>
       <c r="F4" s="9">
-        <v>309651</v>
+        <v>292526</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3">
-        <v>47804</v>
+        <v>39015</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -649,25 +649,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="2">
-        <v>46051</v>
+        <v>46182</v>
       </c>
       <c r="E5" s="2">
-        <v>46053</v>
+        <v>46184</v>
       </c>
       <c r="F5" s="9">
-        <v>314779</v>
+        <v>290318</v>
       </c>
       <c r="G5">
         <v>24</v>
       </c>
       <c r="H5" s="3">
-        <v>20873</v>
+        <v>122655</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -675,234 +675,82 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="2">
-        <v>46051</v>
+        <v>46182</v>
       </c>
       <c r="E6" s="2">
-        <v>46053</v>
+        <v>46184</v>
       </c>
       <c r="F6" s="9">
-        <v>309652</v>
+        <v>290317</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3">
-        <v>47804</v>
+        <v>122655</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F7" s="9">
-        <v>292527</v>
-      </c>
-      <c r="G7">
-        <v>18</v>
-      </c>
-      <c r="H7" s="3">
-        <v>60800</v>
-      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="9"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E8" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F8" s="8">
-        <v>314780</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3">
-        <v>20873</v>
-      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="8"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F9" s="8">
-        <v>292526</v>
-      </c>
-      <c r="G9">
-        <v>20</v>
-      </c>
-      <c r="H9" s="3">
-        <v>60800</v>
-      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="8"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E10" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F10" s="8">
-        <v>300866</v>
-      </c>
-      <c r="G10">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3">
-        <v>31643</v>
-      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="8"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E11" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F11" s="8">
-        <v>314781</v>
-      </c>
-      <c r="G11">
-        <v>20</v>
-      </c>
-      <c r="H11" s="3">
-        <v>48838</v>
-      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="8"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F12" s="8">
-        <v>314782</v>
-      </c>
-      <c r="G12">
-        <v>20</v>
-      </c>
-      <c r="H12" s="3">
-        <v>48838</v>
-      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="8"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E13" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F13" s="8">
-        <v>300864</v>
-      </c>
-      <c r="G13">
-        <v>12</v>
-      </c>
-      <c r="H13" s="3">
-        <v>104318</v>
-      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="8"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="2">
-        <v>46051</v>
-      </c>
-      <c r="E14" s="2">
-        <v>46053</v>
-      </c>
-      <c r="F14" s="8">
-        <v>300863</v>
-      </c>
-      <c r="G14">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3">
-        <v>95045</v>
-      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/đơn hàng tay.xlsx
+++ b/đơn hàng tay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\code py\Xử lý đơn hàng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C51450-A831-477F-BFDD-C727C2050528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D468CC36-451C-4150-9FF5-61DC35B03BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-615" yWindow="2940" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1305" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -109,7 +109,7 @@
     <t>C6/27 Phạm Hùng, Xã Bình Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
-    <t>P-000229637</t>
+    <t>P-000243499</t>
   </si>
 </sst>
 </file>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +151,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Courier"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times-Bold"/>
     </font>
   </fonts>
   <fills count="2">
@@ -189,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -208,6 +214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -528,7 +535,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" customWidth="1"/>
@@ -540,7 +547,7 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -566,186 +573,262 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="2">
-        <v>46182</v>
+        <v>46197</v>
       </c>
       <c r="E2" s="2">
-        <v>46184</v>
+        <v>46199</v>
       </c>
       <c r="F2" s="9">
-        <v>290320</v>
+        <v>300865</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H2" s="3">
-        <v>35360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>10221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>46182</v>
+        <v>46197</v>
       </c>
       <c r="E3" s="2">
-        <v>46184</v>
+        <v>46199</v>
       </c>
       <c r="F3" s="9">
-        <v>290321</v>
+        <v>290320</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H3" s="3">
         <v>35360</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>46182</v>
+        <v>46197</v>
       </c>
       <c r="E4" s="2">
-        <v>46184</v>
+        <v>46199</v>
       </c>
       <c r="F4" s="9">
-        <v>292526</v>
+        <v>290316</v>
       </c>
       <c r="G4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3">
-        <v>39015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>131673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="2">
-        <v>46182</v>
+        <v>46197</v>
       </c>
       <c r="E5" s="2">
-        <v>46184</v>
+        <v>46199</v>
       </c>
       <c r="F5" s="9">
-        <v>290318</v>
+        <v>290315</v>
       </c>
       <c r="G5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H5" s="3">
-        <v>122655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>131673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="2">
-        <v>46182</v>
+        <v>46197</v>
       </c>
       <c r="E6" s="2">
-        <v>46184</v>
+        <v>46199</v>
       </c>
       <c r="F6" s="9">
+        <v>315320</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6" s="3">
+        <v>61286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46199</v>
+      </c>
+      <c r="F7" s="9">
+        <v>300866</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7" s="3">
+        <v>34808</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46199</v>
+      </c>
+      <c r="F8" s="8">
+        <v>300867</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
+        <v>107100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46199</v>
+      </c>
+      <c r="F9" s="8">
         <v>290317</v>
       </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3">
         <v>122655</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="7"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="9"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C8" s="7"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="8"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="7"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="8"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="7"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="8"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="7"/>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46197</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46199</v>
+      </c>
+      <c r="F10" s="8">
+        <v>290318</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3">
+        <v>122655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16.5">
+      <c r="C11" s="10"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="8"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="7"/>
+    <row r="12" spans="1:8" ht="16.5">
+      <c r="C12" s="10"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="8"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="C13" s="7"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="8"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="C14" s="7"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -762,13 +845,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4FD15D-6A49-4832-8B5E-C8EAB0E6A5D6}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="35.140625" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -782,7 +865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -796,7 +879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -810,7 +893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -824,7 +907,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>

--- a/đơn hàng tay.xlsx
+++ b/đơn hàng tay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\code py\Xử lý đơn hàng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D468CC36-451C-4150-9FF5-61DC35B03BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349476C0-E391-4BFA-B1D2-63FC7AD6D55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1305" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1935" yWindow="1980" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -109,7 +109,13 @@
     <t>C6/27 Phạm Hùng, Xã Bình Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
-    <t>P-000243499</t>
+    <t>P-000244377</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>P-000231021</t>
   </si>
 </sst>
 </file>
@@ -120,7 +126,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,13 +156,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Courier"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Times-Bold"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -207,14 +214,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -534,8 +541,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" customWidth="1"/>
@@ -547,7 +554,7 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -573,267 +580,325 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E2" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F2" s="9">
-        <v>300865</v>
+        <v>46214</v>
+      </c>
+      <c r="F2" s="8">
+        <v>300868</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H2" s="3">
-        <v>10221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>107100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E3" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F3" s="9">
-        <v>290320</v>
+        <v>46214</v>
+      </c>
+      <c r="F3" s="8">
+        <v>300867</v>
       </c>
       <c r="G3">
         <v>12</v>
       </c>
       <c r="H3" s="3">
-        <v>35360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>107100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E4" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F4" s="9">
-        <v>290316</v>
+        <v>46214</v>
+      </c>
+      <c r="F4" s="8">
+        <v>315320</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3">
-        <v>131673</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>61286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E5" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F5" s="9">
-        <v>290315</v>
+        <v>46214</v>
+      </c>
+      <c r="F5" s="8">
+        <v>290317</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3">
-        <v>131673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>130832</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E6" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F6" s="9">
-        <v>315320</v>
+        <v>46214</v>
+      </c>
+      <c r="F6" s="8">
+        <v>290318</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3">
-        <v>61286</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>130832</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E7" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F7" s="9">
-        <v>300866</v>
+        <v>46214</v>
+      </c>
+      <c r="F7" s="8">
+        <v>290315</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3">
-        <v>34808</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>131673</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E8" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F8" s="8">
-        <v>300867</v>
+        <v>46214</v>
+      </c>
+      <c r="F8" s="7">
+        <v>290316</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8" s="3">
-        <v>107100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>131673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="2">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="E9" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F9" s="8">
-        <v>290317</v>
+        <v>46214</v>
+      </c>
+      <c r="F9" s="7">
+        <v>300865</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3">
-        <v>122655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>10221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D10" s="2">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="E10" s="2">
-        <v>46199</v>
-      </c>
-      <c r="F10" s="8">
-        <v>290318</v>
+        <v>46214</v>
+      </c>
+      <c r="F10" s="7">
+        <v>315320</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3">
-        <v>122655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.5">
-      <c r="C11" s="10"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="8"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="16.5">
-      <c r="C12" s="10"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="8"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="C13" s="7"/>
+        <v>61286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46211</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F11" s="8">
+        <v>300868</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11" s="3">
+        <v>107100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46211</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F12" s="8">
+        <v>300867</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12" s="3">
+        <v>107100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="9"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="7"/>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
-      <c r="C14" s="7"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="8"/>
-      <c r="H14" s="3"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="10"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="10"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="10"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="10"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -845,13 +910,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4FD15D-6A49-4832-8B5E-C8EAB0E6A5D6}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.140625" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -865,7 +930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75">
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -879,7 +944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75">
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -893,7 +958,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -907,7 +972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>

--- a/đơn hàng tay.xlsx
+++ b/đơn hàng tay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\code py\Xử lý đơn hàng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349476C0-E391-4BFA-B1D2-63FC7AD6D55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC4EFAF-9F65-40D9-98B4-992C2372E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="1980" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2955" yWindow="1890" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -109,13 +109,10 @@
     <t>C6/27 Phạm Hùng, Xã Bình Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
-    <t>P-000244377</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>P-000231021</t>
+    <t>P-000245207</t>
+  </si>
+  <si>
+    <t>P-000231645</t>
   </si>
 </sst>
 </file>
@@ -541,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -591,19 +588,19 @@
         <v>23</v>
       </c>
       <c r="D2" s="2">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="E2" s="2">
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="F2" s="8">
-        <v>300868</v>
+        <v>309651</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H2" s="3">
-        <v>107100</v>
+        <v>52585</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -617,19 +614,19 @@
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="E3" s="2">
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="F3" s="8">
-        <v>300867</v>
+        <v>309652</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3">
-        <v>107100</v>
+        <v>52585</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -643,10 +640,10 @@
         <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="E4" s="2">
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="F4" s="8">
         <v>315320</v>
@@ -669,19 +666,19 @@
         <v>23</v>
       </c>
       <c r="D5" s="2">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="E5" s="2">
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="F5" s="8">
-        <v>290317</v>
+        <v>300868</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3">
-        <v>130832</v>
+        <v>107100</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -695,19 +692,19 @@
         <v>23</v>
       </c>
       <c r="D6" s="2">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="E6" s="2">
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="F6" s="8">
-        <v>290318</v>
+        <v>314780</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6" s="3">
-        <v>130832</v>
+        <v>20873</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -721,19 +718,19 @@
         <v>23</v>
       </c>
       <c r="D7" s="2">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="E7" s="2">
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="F7" s="8">
-        <v>290315</v>
+        <v>300865</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3">
-        <v>131673</v>
+        <v>12580</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -741,25 +738,25 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2">
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="E8" s="2">
-        <v>46214</v>
+        <v>46234</v>
       </c>
       <c r="F8" s="7">
-        <v>290316</v>
+        <v>309651</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3">
-        <v>131673</v>
+        <v>52585</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -767,25 +764,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="E9" s="2">
-        <v>46214</v>
-      </c>
-      <c r="F9" s="7">
-        <v>300865</v>
+        <v>46234</v>
+      </c>
+      <c r="F9" s="8">
+        <v>309652</v>
       </c>
       <c r="G9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H9" s="3">
-        <v>10221</v>
+        <v>52585</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -796,19 +793,19 @@
         <v>22</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="E10" s="2">
-        <v>46214</v>
-      </c>
-      <c r="F10" s="7">
+        <v>46234</v>
+      </c>
+      <c r="F10" s="8">
         <v>315320</v>
       </c>
       <c r="G10">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3">
         <v>61286</v>
@@ -822,22 +819,22 @@
         <v>22</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="E11" s="2">
-        <v>46214</v>
-      </c>
-      <c r="F11" s="8">
-        <v>300868</v>
+        <v>46234</v>
+      </c>
+      <c r="F11" s="7">
+        <v>290317</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="3">
-        <v>107100</v>
+        <v>130832</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -848,42 +845,127 @@
         <v>22</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="E12" s="2">
-        <v>46214</v>
-      </c>
-      <c r="F12" s="8">
-        <v>300867</v>
+        <v>46234</v>
+      </c>
+      <c r="F12" s="7">
+        <v>290318</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="3">
-        <v>107100</v>
+        <v>130832</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C13" s="9"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="7"/>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3"/>
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46224</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46234</v>
+      </c>
+      <c r="F13" s="7">
+        <v>300865</v>
+      </c>
+      <c r="G13">
+        <v>24</v>
+      </c>
+      <c r="H13" s="3">
+        <v>12580</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="10"/>
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46224</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46234</v>
+      </c>
+      <c r="F14" s="7">
+        <v>300866</v>
+      </c>
+      <c r="G14">
+        <v>24</v>
+      </c>
+      <c r="H14" s="3">
+        <v>42840</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="10"/>
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46224</v>
+      </c>
+      <c r="E15" s="2">
+        <v>46234</v>
+      </c>
+      <c r="F15" s="7">
+        <v>305434</v>
+      </c>
+      <c r="G15">
+        <v>12</v>
+      </c>
+      <c r="H15" s="3">
+        <v>81600</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="10"/>
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46224</v>
+      </c>
+      <c r="E16" s="2">
+        <v>46234</v>
+      </c>
+      <c r="F16" s="7">
+        <v>305435</v>
+      </c>
+      <c r="G16">
+        <v>12</v>
+      </c>
+      <c r="H16" s="3">
+        <v>81600</v>
+      </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="10"/>
@@ -893,12 +975,6 @@
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" s="10"/>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="10"/>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/đơn hàng tay.xlsx
+++ b/đơn hàng tay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\code py\Xử lý đơn hàng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC4EFAF-9F65-40D9-98B4-992C2372E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A158FA07-F19D-452F-A561-71156131B751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="1890" windowWidth="23625" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -109,10 +109,7 @@
     <t>C6/27 Phạm Hùng, Xã Bình Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
-    <t>P-000245207</t>
-  </si>
-  <si>
-    <t>P-000231645</t>
+    <t>P-000232421</t>
   </si>
 </sst>
 </file>
@@ -199,7 +196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -212,9 +209,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -538,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -582,25 +576,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="2">
-        <v>46227</v>
+        <v>46240</v>
       </c>
       <c r="E2" s="2">
-        <v>46228</v>
-      </c>
-      <c r="F2" s="8">
-        <v>309651</v>
+        <v>46242</v>
+      </c>
+      <c r="F2" s="7">
+        <v>314781</v>
       </c>
       <c r="G2">
         <v>20</v>
       </c>
       <c r="H2" s="3">
-        <v>52585</v>
+        <v>45082</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -608,25 +602,25 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>46227</v>
+        <v>46240</v>
       </c>
       <c r="E3" s="2">
-        <v>46228</v>
-      </c>
-      <c r="F3" s="8">
-        <v>309652</v>
+        <v>46242</v>
+      </c>
+      <c r="F3">
+        <v>292526</v>
       </c>
       <c r="G3">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3">
-        <v>52585</v>
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>39015</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -634,347 +628,29 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>46227</v>
+        <v>46240</v>
       </c>
       <c r="E4" s="2">
-        <v>46228</v>
-      </c>
-      <c r="F4" s="8">
-        <v>315320</v>
+        <v>46242</v>
+      </c>
+      <c r="F4">
+        <v>292527</v>
       </c>
       <c r="G4">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3">
-        <v>61286</v>
+        <v>12</v>
+      </c>
+      <c r="H4">
+        <v>39015</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46227</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46228</v>
-      </c>
-      <c r="F5" s="8">
-        <v>300868</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3">
-        <v>107100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46227</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46228</v>
-      </c>
-      <c r="F6" s="8">
-        <v>314780</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6" s="3">
-        <v>20873</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46227</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46228</v>
-      </c>
-      <c r="F7" s="8">
-        <v>300865</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7" s="3">
-        <v>12580</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E8" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F8" s="7">
-        <v>309651</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8" s="3">
-        <v>52585</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F9" s="8">
-        <v>309652</v>
-      </c>
-      <c r="G9">
-        <v>20</v>
-      </c>
-      <c r="H9" s="3">
-        <v>52585</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E10" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F10" s="8">
-        <v>315320</v>
-      </c>
-      <c r="G10">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3">
-        <v>61286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E11" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F11" s="7">
-        <v>290317</v>
-      </c>
-      <c r="G11">
-        <v>20</v>
-      </c>
-      <c r="H11" s="3">
-        <v>130832</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F12" s="7">
-        <v>290318</v>
-      </c>
-      <c r="G12">
-        <v>20</v>
-      </c>
-      <c r="H12" s="3">
-        <v>130832</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E13" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F13" s="7">
-        <v>300865</v>
-      </c>
-      <c r="G13">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3">
-        <v>12580</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E14" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F14" s="7">
-        <v>300866</v>
-      </c>
-      <c r="G14">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3">
-        <v>42840</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E15" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F15" s="7">
-        <v>305434</v>
-      </c>
-      <c r="G15">
-        <v>12</v>
-      </c>
-      <c r="H15" s="3">
-        <v>81600</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="2">
-        <v>46224</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46234</v>
-      </c>
-      <c r="F16" s="7">
-        <v>305435</v>
-      </c>
-      <c r="G16">
-        <v>12</v>
-      </c>
-      <c r="H16" s="3">
-        <v>81600</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="10"/>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="10"/>
+      <c r="C5" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/đơn hàng tay.xlsx
+++ b/đơn hàng tay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\code py\Xử lý đơn hàng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A158FA07-F19D-452F-A561-71156131B751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F00E3F-5067-43B4-816C-D98BB4CA1754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5610" yWindow="2310" windowWidth="17850" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>Hệ thống</t>
   </si>
@@ -109,7 +109,7 @@
     <t>C6/27 Phạm Hùng, Xã Bình Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
   </si>
   <si>
-    <t>P-000232421</t>
+    <t>P-000233110</t>
   </si>
 </sst>
 </file>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,12 +150,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -196,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -208,11 +202,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -578,23 +568,23 @@
       <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="2">
-        <v>46240</v>
+        <v>46254</v>
       </c>
       <c r="E2" s="2">
-        <v>46242</v>
-      </c>
-      <c r="F2" s="7">
-        <v>314781</v>
+        <v>46258</v>
+      </c>
+      <c r="F2">
+        <v>290317</v>
       </c>
       <c r="G2">
         <v>20</v>
       </c>
       <c r="H2" s="3">
-        <v>45082</v>
+        <v>163540</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -604,53 +594,34 @@
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>46240</v>
+        <v>46254</v>
       </c>
       <c r="E3" s="2">
-        <v>46242</v>
+        <v>46258</v>
       </c>
       <c r="F3">
-        <v>292526</v>
+        <v>290318</v>
       </c>
       <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3">
-        <v>39015</v>
+        <v>20</v>
+      </c>
+      <c r="H3" s="3">
+        <v>163540</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46240</v>
-      </c>
-      <c r="E4" s="2">
-        <v>46242</v>
-      </c>
-      <c r="F4">
-        <v>292527</v>
-      </c>
-      <c r="G4">
-        <v>12</v>
-      </c>
-      <c r="H4">
-        <v>39015</v>
-      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="9"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
